--- a/utils/monday_sprint_sprint_2025-12.xlsx
+++ b/utils/monday_sprint_sprint_2025-12.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="240">
   <si>
     <t>Ticket</t>
   </si>
@@ -105,7 +105,7 @@
     <t>26/03/2024</t>
   </si>
   <si>
-    <t>25/03/2026</t>
+    <t>20/03/2026</t>
   </si>
   <si>
     <t>Semana 4</t>
@@ -399,7 +399,7 @@
     <t>15/05/2025</t>
   </si>
   <si>
-    <t>15/04/2026</t>
+    <t>10/04/2026</t>
   </si>
   <si>
     <t>Maio</t>
@@ -426,7 +426,7 @@
     <t>25/04/2023</t>
   </si>
   <si>
-    <t>23/02/2026</t>
+    <t>18/02/2026</t>
   </si>
   <si>
     <t>Abril</t>
@@ -471,6 +471,9 @@
     <t>10/02/2025</t>
   </si>
   <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
     <t>Semana 2</t>
   </si>
   <si>
@@ -498,7 +501,7 @@
     <t>24/10/2024</t>
   </si>
   <si>
-    <t>22/03/2026</t>
+    <t>17/03/2026</t>
   </si>
   <si>
     <t>Outubro</t>
@@ -3482,51 +3485,51 @@
         <v>151</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>17</v>
+        <v>152</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>126</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>20</v>
@@ -3535,12 +3538,12 @@
         <v>31</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>15</v>
@@ -3552,10 +3555,10 @@
         <v>17</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>19</v>
@@ -3573,7 +3576,7 @@
         <v>17</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M55" s="2" t="s">
         <v>41</v>
@@ -3584,7 +3587,7 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>15</v>
@@ -3596,10 +3599,10 @@
         <v>17</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>19</v>
@@ -3628,7 +3631,7 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>15</v>
@@ -3640,10 +3643,10 @@
         <v>24</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>19</v>
@@ -3655,10 +3658,10 @@
         <v>28</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>17</v>
+        <v>152</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>35</v>
@@ -3667,12 +3670,12 @@
         <v>61</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>15</v>
@@ -3684,10 +3687,10 @@
         <v>17</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>19</v>
@@ -3716,7 +3719,7 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>15</v>
@@ -3728,10 +3731,10 @@
         <v>17</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>19</v>
@@ -3760,7 +3763,7 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>15</v>
@@ -3772,10 +3775,10 @@
         <v>17</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>19</v>
@@ -3804,7 +3807,7 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>15</v>
@@ -3816,10 +3819,10 @@
         <v>17</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>19</v>
@@ -3848,7 +3851,7 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>15</v>
@@ -3860,10 +3863,10 @@
         <v>17</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>19</v>
@@ -3892,7 +3895,7 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>15</v>
@@ -3904,10 +3907,10 @@
         <v>17</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>19</v>
@@ -3936,7 +3939,7 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>15</v>
@@ -3948,10 +3951,10 @@
         <v>17</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>19</v>
@@ -3980,7 +3983,7 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>15</v>
@@ -3992,10 +3995,10 @@
         <v>17</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>49</v>
@@ -4024,7 +4027,7 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>15</v>
@@ -4036,10 +4039,10 @@
         <v>17</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>19</v>
@@ -4068,7 +4071,7 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>15</v>
@@ -4080,10 +4083,10 @@
         <v>17</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>19</v>
@@ -4112,22 +4115,22 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>19</v>
@@ -4156,22 +4159,22 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>19</v>
@@ -4200,22 +4203,22 @@
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>19</v>
@@ -4244,22 +4247,22 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>19</v>
@@ -4288,22 +4291,22 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>19</v>
@@ -4332,22 +4335,22 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>19</v>
@@ -4376,7 +4379,7 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>15</v>
@@ -4388,10 +4391,10 @@
         <v>24</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>19</v>
@@ -4403,10 +4406,10 @@
         <v>28</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>17</v>
+        <v>152</v>
       </c>
       <c r="L74" s="2" t="s">
         <v>20</v>
@@ -4415,12 +4418,12 @@
         <v>61</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>15</v>
@@ -4432,10 +4435,10 @@
         <v>17</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>19</v>
@@ -4464,7 +4467,7 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>15</v>
@@ -4476,10 +4479,10 @@
         <v>17</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>19</v>
@@ -4508,7 +4511,7 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>15</v>
@@ -4520,10 +4523,10 @@
         <v>17</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>19</v>
@@ -4552,7 +4555,7 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>15</v>
@@ -4564,10 +4567,10 @@
         <v>17</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>19</v>
@@ -4608,10 +4611,10 @@
         <v>17</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>19</v>
@@ -4652,10 +4655,10 @@
         <v>17</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>19</v>
@@ -4695,23 +4698,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -4719,16 +4722,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -4747,7 +4750,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -4760,7 +4763,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K23">
         <v>1</v>
@@ -4768,7 +4771,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -4799,12 +4802,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B2">
         <v>79</v>
@@ -4828,25 +4831,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -4863,13 +4866,13 @@
         <v>59</v>
       </c>
       <c r="G10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -4901,7 +4904,7 @@
         <v>7</v>
       </c>
       <c r="J11" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K11">
         <v>79</v>
@@ -4913,7 +4916,7 @@
         <v>11</v>
       </c>
       <c r="P11" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q11">
         <v>1</v>
@@ -4921,7 +4924,7 @@
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E12">
         <v>6</v>
@@ -4933,7 +4936,7 @@
         <v>71</v>
       </c>
       <c r="M12" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -4942,7 +4945,7 @@
         <v>21</v>
       </c>
       <c r="Q12">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
@@ -4965,36 +4968,30 @@
         <v>12</v>
       </c>
       <c r="P13" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="Q13">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="4:17" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N14">
         <v>1</v>
-      </c>
-      <c r="P14" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q14">
-        <v>24</v>
       </c>
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
@@ -5007,7 +5004,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -5015,7 +5012,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -5023,7 +5020,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -5034,7 +5031,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -5048,7 +5045,7 @@
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>133</v>
@@ -5062,7 +5059,7 @@
         <v>15</v>
       </c>
       <c r="F22" s="2">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>139</v>
@@ -5076,7 +5073,7 @@
         <v>15</v>
       </c>
       <c r="F23" s="2">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>25</v>
@@ -5084,35 +5081,35 @@
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F24" s="2">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F25" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>15</v>
@@ -5121,7 +5118,7 @@
         <v>458</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5132,7 +5129,7 @@
         <v>15</v>
       </c>
       <c r="F27" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>148</v>
@@ -5146,7 +5143,7 @@
         <v>15</v>
       </c>
       <c r="F28" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>123</v>

--- a/utils/monday_sprint_sprint_2025-12.xlsx
+++ b/utils/monday_sprint_sprint_2025-12.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1285" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1285" uniqueCount="266">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>23838</t>
+    <t>9189848836</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>20/05/2025</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>03/06/2025</t>
   </si>
   <si>
     <t>Feito</t>
@@ -105,6 +105,9 @@
     <t>25311</t>
   </si>
   <si>
+    <t>Logística</t>
+  </si>
+  <si>
     <t>Melhoria</t>
   </si>
   <si>
@@ -132,7 +135,7 @@
     <t>Semana 4</t>
   </si>
   <si>
-    <t>31609</t>
+    <t>9170146829</t>
   </si>
   <si>
     <t>ALERTA DE REVISÃO X BLOQUEIO DE MODELO</t>
@@ -141,27 +144,24 @@
     <t>16/05/2025</t>
   </si>
   <si>
+    <t>02/06/2025</t>
+  </si>
+  <si>
     <t>A fazer</t>
   </si>
   <si>
-    <t>Aberto</t>
-  </si>
-  <si>
-    <t>31436</t>
+    <t>9170567273</t>
   </si>
   <si>
     <t>Fotos - Registro de Inspeção - Reunião</t>
   </si>
   <si>
-    <t>31682</t>
+    <t>9279434797</t>
   </si>
   <si>
     <t>Revisão de Pontos</t>
   </si>
   <si>
-    <t>02/06/2025</t>
-  </si>
-  <si>
     <t>Fazendo</t>
   </si>
   <si>
@@ -171,7 +171,7 @@
     <t>Junho</t>
   </si>
   <si>
-    <t>31225</t>
+    <t>9067814016</t>
   </si>
   <si>
     <t>Alteração no Preenchimento dos Certificados no AP119 - Reunião</t>
@@ -180,7 +180,10 @@
     <t>05/05/2025</t>
   </si>
   <si>
-    <t>31621</t>
+    <t>14/06/2025</t>
+  </si>
+  <si>
+    <t>9170044979</t>
   </si>
   <si>
     <t>Irog ajustagem</t>
@@ -189,7 +192,10 @@
     <t>Baixa</t>
   </si>
   <si>
-    <t>31702</t>
+    <t>09/06/2025</t>
+  </si>
+  <si>
+    <t>9171543409</t>
   </si>
   <si>
     <t>Migração de licenças para SAAS - Licença gerentes</t>
@@ -198,7 +204,10 @@
     <t>Alta</t>
   </si>
   <si>
-    <t>30905</t>
+    <t>08/06/2025</t>
+  </si>
+  <si>
+    <t>9180178135</t>
   </si>
   <si>
     <t>ACVO - REUNIÃO</t>
@@ -207,7 +216,7 @@
     <t>19/05/2025</t>
   </si>
   <si>
-    <t>31092</t>
+    <t>8956510746</t>
   </si>
   <si>
     <t>Etiquetas corpo de prova</t>
@@ -216,25 +225,28 @@
     <t>17/04/2025</t>
   </si>
   <si>
+    <t>10/06/2025</t>
+  </si>
+  <si>
     <t>Homologação</t>
   </si>
   <si>
     <t>Abril</t>
   </si>
   <si>
-    <t>25807</t>
+    <t>9279286423</t>
   </si>
   <si>
     <t>Apresentação Faseamento</t>
   </si>
   <si>
-    <t>30019</t>
+    <t>9180073160</t>
   </si>
   <si>
     <t>Peças em carteira - Ultimo fornecimento +4 anos</t>
   </si>
   <si>
-    <t>32007</t>
+    <t>9269509145</t>
   </si>
   <si>
     <t>Geração de relatório - Notas de entrada</t>
@@ -243,28 +255,31 @@
     <t>30/05/2025</t>
   </si>
   <si>
+    <t>04/06/2025</t>
+  </si>
+  <si>
     <t>Semana 5</t>
   </si>
   <si>
-    <t>32002</t>
+    <t>9269539739</t>
   </si>
   <si>
     <t>Apontamento IROG-BI moldagem USE</t>
   </si>
   <si>
-    <t>31996</t>
+    <t>9269644008</t>
   </si>
   <si>
     <t>Falha quantidade blocos de prova</t>
   </si>
   <si>
-    <t>31984</t>
+    <t>9269664065</t>
   </si>
   <si>
     <t>Projeto Revisão FTF - Documentação de Cálculo</t>
   </si>
   <si>
-    <t>31977</t>
+    <t>9269682452</t>
   </si>
   <si>
     <t>Alterações no registro de moldagem via APP</t>
@@ -273,100 +288,106 @@
     <t>Testes</t>
   </si>
   <si>
-    <t>31961</t>
+    <t>9269805334</t>
   </si>
   <si>
     <t>LIBERAR REVISÕES NO C.P.P</t>
   </si>
   <si>
-    <t>31950</t>
+    <t>9269815810</t>
   </si>
   <si>
     <t>Incluir informação - Relatório de Moldagens</t>
   </si>
   <si>
-    <t>31948</t>
+    <t>9269824240</t>
   </si>
   <si>
     <t>Melhoria Sist. Embalagens</t>
   </si>
   <si>
-    <t>31935</t>
+    <t>9269832339</t>
   </si>
   <si>
     <t>WMS - Ordem de Movimentação</t>
   </si>
   <si>
-    <t>31933</t>
+    <t>15/06/2025</t>
+  </si>
+  <si>
+    <t>9269847898</t>
   </si>
   <si>
     <t>WMS - Tela de Pick List</t>
   </si>
   <si>
-    <t>31921</t>
+    <t>9269856993</t>
   </si>
   <si>
     <t>Trava Tipo de Vcto Invoice</t>
   </si>
   <si>
-    <t>31911</t>
+    <t>9270301000</t>
   </si>
   <si>
     <t>Mudanças no Posto de cópias eletrônico</t>
   </si>
   <si>
-    <t>31896</t>
+    <t>9270347540</t>
   </si>
   <si>
     <t>Melhoria sistema corridas</t>
   </si>
   <si>
-    <t>31892</t>
+    <t>9270360301</t>
   </si>
   <si>
     <t>FORMULÁRIO GERAL DE ANÁLISE CRÍTICA</t>
   </si>
   <si>
-    <t>31889</t>
+    <t>9270370188</t>
   </si>
   <si>
     <t>ALERTA DE DEVOLUÇÃO DE PEÇAS</t>
   </si>
   <si>
-    <t>31884</t>
+    <t>9270382492</t>
   </si>
   <si>
     <t>Melhoria do formulário 596</t>
   </si>
   <si>
-    <t>31876</t>
+    <t>9270395357</t>
   </si>
   <si>
     <t>Alteração no sistema de orçamento</t>
   </si>
   <si>
-    <t>31855</t>
+    <t>9270402604</t>
   </si>
   <si>
     <t>Tela de Transferência</t>
   </si>
   <si>
+    <t>9280294611</t>
+  </si>
+  <si>
     <t>Migração de licenças para SAAS - Licença Coordenadores</t>
   </si>
   <si>
-    <t>31852</t>
+    <t>9270429256</t>
   </si>
   <si>
     <t>Apontamento - Altona Engenharia</t>
   </si>
   <si>
-    <t>31844</t>
+    <t>9270437462</t>
   </si>
   <si>
     <t>Alteração na visualização dos lote de ferro liga</t>
   </si>
   <si>
-    <t>31835</t>
+    <t>9270500579</t>
   </si>
   <si>
     <t>Correção</t>
@@ -375,54 +396,57 @@
     <t>computador de apontamento rebarbação VI</t>
   </si>
   <si>
-    <t>31827</t>
+    <t>9270518192</t>
   </si>
   <si>
     <t>Registro e relatório de liquido penetrante</t>
   </si>
   <si>
-    <t>31822</t>
+    <t>9270535672</t>
   </si>
   <si>
     <t>Solicitação de Exclusão do Botão "Dar Entrada" no Sistema SPS</t>
   </si>
   <si>
-    <t>31765</t>
+    <t>9270583759</t>
   </si>
   <si>
     <t>B.I. Inspeção</t>
   </si>
   <si>
-    <t>31760</t>
+    <t>9270610892</t>
   </si>
   <si>
     <t>Embalagem pendente</t>
   </si>
   <si>
-    <t>31758</t>
+    <t>9270620621</t>
   </si>
   <si>
     <t>Ajustes de quantidade no inventário via coletor</t>
   </si>
   <si>
-    <t>31753</t>
+    <t>9270650682</t>
   </si>
   <si>
     <t>Criar códigos de paradas</t>
   </si>
   <si>
-    <t>31723</t>
+    <t>9270681248</t>
   </si>
   <si>
     <t>Implementar funcionalidade para replicação de conta contábil em lançamentos sem OC</t>
   </si>
   <si>
-    <t>31708</t>
+    <t>9270695454</t>
   </si>
   <si>
     <t>Cadastro de Checklist eletrônico - auditoria ambiental</t>
   </si>
   <si>
+    <t>9280300708</t>
+  </si>
+  <si>
     <t>Migração de licenças para SAAS - Licença Supervisores</t>
   </si>
   <si>
@@ -447,33 +471,42 @@
     <t>10/04/2026</t>
   </si>
   <si>
-    <t>31248</t>
+    <t>9270762127</t>
   </si>
   <si>
     <t>Sites Internos de Sistemas - Servidor IIS</t>
   </si>
   <si>
-    <t>19909</t>
+    <t>9279273705</t>
   </si>
   <si>
     <t>Consulta Registros</t>
   </si>
   <si>
+    <t>9279273820</t>
+  </si>
+  <si>
     <t>Consulta do Log</t>
   </si>
   <si>
-    <t>32298</t>
+    <t>12/06/2025</t>
+  </si>
+  <si>
+    <t>9279327189</t>
   </si>
   <si>
     <t>Protótipo mapeamento de solda</t>
   </si>
   <si>
-    <t>29095</t>
+    <t>9279327467</t>
   </si>
   <si>
     <t>Diário do bordo Ajustagem - Leitura de Tempo por Cabine</t>
   </si>
   <si>
+    <t>9280095361</t>
+  </si>
+  <si>
     <t>Diário do bordo Ajustagem - Informativo Cabine</t>
   </si>
   <si>
@@ -486,6 +519,9 @@
     <t>30012</t>
   </si>
   <si>
+    <t>PCP</t>
+  </si>
+  <si>
     <t>Saneamento de dados para APS e treinamento</t>
   </si>
   <si>
@@ -501,9 +537,6 @@
     <t>28569</t>
   </si>
   <si>
-    <t>PCP</t>
-  </si>
-  <si>
     <t>Análise</t>
   </si>
   <si>
@@ -522,7 +555,7 @@
     <t>17/03/2026</t>
   </si>
   <si>
-    <t>28583</t>
+    <t>9280379506</t>
   </si>
   <si>
     <t>Compara Carteira UPR - Erro</t>
@@ -531,7 +564,7 @@
     <t>Implantação</t>
   </si>
   <si>
-    <t>24746</t>
+    <t>9279502552</t>
   </si>
   <si>
     <t>Integração de faturamentos com eventos</t>
@@ -546,84 +579,105 @@
     <t>Boa tarde Conforme conversamos, precisamos de um sistema dentro do WMS que faça a distribuição em tempo real do saldo do Estoque com a carteira. Conforme é realizado o faturamento, a carteira seja atualizada em tempo real, bem como a entrada e estorno do material. O sistema deve fornecer um relatóri</t>
   </si>
   <si>
-    <t>31233</t>
+    <t>9279518138</t>
   </si>
   <si>
     <t>Integração faturamento x Benner  Reunião de entrega</t>
   </si>
   <si>
+    <t>9279549006</t>
+  </si>
+  <si>
     <t>Ao vincular NF na invoice (no sistema Altona), atualizar esta informação no Benner</t>
   </si>
   <si>
-    <t>31529</t>
+    <t>9279608051</t>
   </si>
   <si>
     <t>Pré-lista em cascata, por endereço</t>
   </si>
   <si>
-    <t>30903</t>
+    <t>9279622212</t>
   </si>
   <si>
     <t>Criação de Sistema de Controle impostos e declarações</t>
   </si>
   <si>
-    <t>31528</t>
+    <t>9279837242</t>
   </si>
   <si>
     <t>E-mail automático - CPC / OTF</t>
   </si>
   <si>
-    <t>31615</t>
+    <t>9279845068</t>
   </si>
   <si>
     <t>Relatório de comissões por invoice por período e representante</t>
   </si>
   <si>
-    <t>31015</t>
+    <t>9280726958</t>
   </si>
   <si>
     <t>Conversão KB TOTO</t>
   </si>
   <si>
-    <t>31292</t>
+    <t>9180648455</t>
   </si>
   <si>
     <t>Apontamento eletrônico corte pó de ferro - Tela de Parada</t>
   </si>
   <si>
-    <t>30796</t>
+    <t>9281444907</t>
   </si>
   <si>
     <t>Sistema gestão de ações</t>
   </si>
   <si>
-    <t>31257</t>
+    <t>11/06/2025</t>
+  </si>
+  <si>
+    <t>9282597996</t>
   </si>
   <si>
     <t>Máquina de Ensaios</t>
   </si>
   <si>
+    <t>9289609806</t>
+  </si>
+  <si>
     <t>Novo Sistema</t>
   </si>
   <si>
     <t>Cadastro de empresa</t>
   </si>
   <si>
-    <t>03/06/2025</t>
+    <t>9289611507</t>
   </si>
   <si>
     <t>Cadastro do tipo de anexos.</t>
   </si>
   <si>
+    <t>9289613393</t>
+  </si>
+  <si>
     <t>Cadastro parâmetros de declarações.</t>
   </si>
   <si>
+    <t>9289614761</t>
+  </si>
+  <si>
     <t>Cadastro de declarações.</t>
   </si>
   <si>
+    <t>9289623089</t>
+  </si>
+  <si>
     <t>Controle de acesso.</t>
   </si>
   <si>
+    <t>9289624369</t>
+  </si>
+  <si>
     <t>Controle do status por declaração</t>
   </si>
   <si>
@@ -639,33 +693,39 @@
     <t>05/06/2025</t>
   </si>
   <si>
-    <t>31791</t>
+    <t>9311790698</t>
   </si>
   <si>
     <t>Correção - Comparativo Pré Embarque</t>
   </si>
   <si>
-    <t>30583</t>
+    <t>9312397510</t>
   </si>
   <si>
     <t>Inventário para o WMS</t>
   </si>
   <si>
-    <t>31226</t>
+    <t>9312409998</t>
   </si>
   <si>
     <t>BUG WMS</t>
   </si>
   <si>
-    <t>30746</t>
+    <t>9312424929</t>
   </si>
   <si>
     <t>Precisamos ajustar a tela Separação Pré-lista</t>
   </si>
   <si>
+    <t>9314754469</t>
+  </si>
+  <si>
     <t>Importar planilha.</t>
   </si>
   <si>
+    <t>9314771918</t>
+  </si>
+  <si>
     <t>Extração planilha / Visualização / Novo item</t>
   </si>
   <si>
@@ -675,7 +735,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2025-12</t>
+    <t>Abr/2025</t>
   </si>
   <si>
     <t>Base</t>
@@ -1284,34 +1344,34 @@
         <v>29</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>25</v>
@@ -1320,7 +1380,7 @@
         <v>26</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>28</v>
@@ -1328,22 +1388,22 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>20</v>
@@ -1355,16 +1415,16 @@
         <v>22</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>27</v>
@@ -1375,22 +1435,22 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>20</v>
@@ -1402,7 +1462,7 @@
         <v>22</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>24</v>
@@ -1422,22 +1482,22 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>20</v>
@@ -1449,16 +1509,16 @@
         <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>49</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>50</v>
@@ -1475,7 +1535,7 @@
         <v>16</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>18</v>
@@ -1499,7 +1559,7 @@
         <v>54</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1516,25 +1576,25 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>21</v>
@@ -1543,10 +1603,10 @@
         <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1563,7 +1623,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1575,13 +1635,13 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>21</v>
@@ -1590,10 +1650,10 @@
         <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>25</v>
@@ -1610,22 +1670,22 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
@@ -1637,16 +1697,16 @@
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>27</v>
@@ -1657,22 +1717,22 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
@@ -1684,42 +1744,42 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
@@ -1731,10 +1791,10 @@
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1751,22 +1811,22 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -1778,16 +1838,16 @@
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
         <v>27</v>
@@ -1798,22 +1858,22 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1825,10 +1885,10 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1837,7 +1897,7 @@
         <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>28</v>
@@ -1845,22 +1905,22 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1872,10 +1932,10 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1884,7 +1944,7 @@
         <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>28</v>
@@ -1892,37 +1952,37 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J16" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1931,7 +1991,7 @@
         <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>28</v>
@@ -1939,22 +1999,22 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -1966,10 +2026,10 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1978,7 +2038,7 @@
         <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>28</v>
@@ -1986,22 +2046,22 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -2013,19 +2073,19 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>28</v>
@@ -2033,22 +2093,22 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -2060,10 +2120,10 @@
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -2072,7 +2132,7 @@
         <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>28</v>
@@ -2080,22 +2140,22 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -2107,10 +2167,10 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -2119,7 +2179,7 @@
         <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>28</v>
@@ -2127,22 +2187,22 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
@@ -2154,10 +2214,10 @@
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -2166,7 +2226,7 @@
         <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>28</v>
@@ -2174,22 +2234,22 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -2201,10 +2261,10 @@
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -2213,7 +2273,7 @@
         <v>26</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>28</v>
@@ -2221,22 +2281,22 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -2248,10 +2308,10 @@
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -2260,7 +2320,7 @@
         <v>26</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>28</v>
@@ -2268,22 +2328,22 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -2295,10 +2355,10 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -2307,7 +2367,7 @@
         <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>28</v>
@@ -2315,37 +2375,37 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="K25" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2354,7 +2414,7 @@
         <v>26</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>28</v>
@@ -2362,22 +2422,22 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2389,10 +2449,10 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
@@ -2401,7 +2461,7 @@
         <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>28</v>
@@ -2409,22 +2469,22 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2436,7 +2496,7 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>24</v>
@@ -2445,10 +2505,10 @@
         <v>49</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>28</v>
@@ -2456,22 +2516,22 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -2483,10 +2543,10 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2495,7 +2555,7 @@
         <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>28</v>
@@ -2503,22 +2563,22 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2530,10 +2590,10 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -2542,7 +2602,7 @@
         <v>26</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>28</v>
@@ -2550,22 +2610,22 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
@@ -2577,10 +2637,10 @@
         <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2589,7 +2649,7 @@
         <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>28</v>
@@ -2597,22 +2657,22 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2624,10 +2684,10 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2636,7 +2696,7 @@
         <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>28</v>
@@ -2644,7 +2704,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>58</v>
+        <v>118</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2656,13 +2716,13 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>21</v>
@@ -2671,10 +2731,10 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2691,22 +2751,22 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
@@ -2718,10 +2778,10 @@
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
@@ -2730,7 +2790,7 @@
         <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="O33" s="2" t="s">
         <v>28</v>
@@ -2738,22 +2798,22 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
@@ -2765,10 +2825,10 @@
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>25</v>
@@ -2777,7 +2837,7 @@
         <v>26</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="O34" s="2" t="s">
         <v>28</v>
@@ -2785,25 +2845,25 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>21</v>
@@ -2812,19 +2872,19 @@
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>49</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="O35" s="2" t="s">
         <v>28</v>
@@ -2832,22 +2892,22 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
@@ -2859,19 +2919,19 @@
         <v>22</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>49</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>28</v>
@@ -2879,22 +2939,22 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>20</v>
@@ -2906,10 +2966,10 @@
         <v>22</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>25</v>
@@ -2918,7 +2978,7 @@
         <v>26</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>28</v>
@@ -2926,22 +2986,22 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>
@@ -2953,10 +3013,10 @@
         <v>22</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>25</v>
@@ -2965,7 +3025,7 @@
         <v>26</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>28</v>
@@ -2973,22 +3033,22 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>20</v>
@@ -3000,10 +3060,10 @@
         <v>22</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>25</v>
@@ -3012,7 +3072,7 @@
         <v>26</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="O39" s="2" t="s">
         <v>28</v>
@@ -3020,22 +3080,22 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>20</v>
@@ -3047,10 +3107,10 @@
         <v>22</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>25</v>
@@ -3059,7 +3119,7 @@
         <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>28</v>
@@ -3067,22 +3127,22 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>20</v>
@@ -3094,19 +3154,19 @@
         <v>22</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="O41" s="2" t="s">
         <v>28</v>
@@ -3114,22 +3174,22 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>20</v>
@@ -3141,10 +3201,10 @@
         <v>22</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>25</v>
@@ -3153,7 +3213,7 @@
         <v>26</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="O42" s="2" t="s">
         <v>28</v>
@@ -3161,22 +3221,22 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>20</v>
@@ -3188,19 +3248,19 @@
         <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="O43" s="2" t="s">
         <v>28</v>
@@ -3208,7 +3268,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>58</v>
+        <v>143</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
@@ -3220,13 +3280,13 @@
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>21</v>
@@ -3235,16 +3295,16 @@
         <v>22</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>49</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="N44" s="2" t="s">
         <v>50</v>
@@ -3255,37 +3315,37 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>25</v>
@@ -3294,7 +3354,7 @@
         <v>26</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="O45" s="2" t="s">
         <v>28</v>
@@ -3302,22 +3362,22 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>20</v>
@@ -3329,19 +3389,19 @@
         <v>22</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="O46" s="2" t="s">
         <v>28</v>
@@ -3349,22 +3409,22 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>20</v>
@@ -3376,16 +3436,16 @@
         <v>22</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="N47" s="2" t="s">
         <v>50</v>
@@ -3396,22 +3456,22 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>20</v>
@@ -3423,10 +3483,10 @@
         <v>22</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>24</v>
+        <v>158</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>25</v>
@@ -3443,7 +3503,7 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>16</v>
@@ -3455,10 +3515,10 @@
         <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>20</v>
@@ -3470,10 +3530,10 @@
         <v>22</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>25</v>
@@ -3490,7 +3550,7 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>16</v>
@@ -3502,10 +3562,10 @@
         <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>20</v>
@@ -3517,16 +3577,16 @@
         <v>22</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>24</v>
+        <v>158</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>49</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="N50" s="2" t="s">
         <v>50</v>
@@ -3537,7 +3597,7 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>16</v>
@@ -3549,13 +3609,13 @@
         <v>18</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>21</v>
@@ -3564,10 +3624,10 @@
         <v>22</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>25</v>
@@ -3584,22 +3644,22 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>20</v>
@@ -3611,10 +3671,10 @@
         <v>22</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>24</v>
+        <v>158</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>25</v>
@@ -3631,37 +3691,37 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>16</v>
+        <v>168</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>25</v>
@@ -3678,37 +3738,37 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>25</v>
@@ -3725,22 +3785,22 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>20</v>
@@ -3752,13 +3812,13 @@
         <v>22</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="M55" s="2" t="s">
         <v>26</v>
@@ -3772,7 +3832,7 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>16</v>
@@ -3784,10 +3844,10 @@
         <v>18</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>20</v>
@@ -3799,16 +3859,16 @@
         <v>22</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="N56" s="2" t="s">
         <v>50</v>
@@ -3819,43 +3879,43 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="N57" s="2" t="s">
         <v>50</v>
@@ -3866,22 +3926,22 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>20</v>
@@ -3893,10 +3953,10 @@
         <v>22</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L58" s="2" t="s">
         <v>25</v>
@@ -3913,22 +3973,22 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>20</v>
@@ -3940,10 +4000,10 @@
         <v>22</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>25</v>
@@ -3960,22 +4020,22 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>20</v>
@@ -3987,16 +4047,16 @@
         <v>22</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="N60" s="2" t="s">
         <v>50</v>
@@ -4007,7 +4067,7 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>16</v>
@@ -4019,10 +4079,10 @@
         <v>18</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>20</v>
@@ -4034,16 +4094,16 @@
         <v>22</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L61" s="2" t="s">
         <v>49</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="N61" s="2" t="s">
         <v>50</v>
@@ -4054,22 +4114,22 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>20</v>
@@ -4081,10 +4141,10 @@
         <v>22</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>24</v>
+        <v>158</v>
       </c>
       <c r="L62" s="2" t="s">
         <v>25</v>
@@ -4101,22 +4161,22 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>20</v>
@@ -4128,16 +4188,16 @@
         <v>22</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>24</v>
+        <v>158</v>
       </c>
       <c r="L63" s="2" t="s">
         <v>49</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="N63" s="2" t="s">
         <v>50</v>
@@ -4148,7 +4208,7 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>16</v>
@@ -4160,10 +4220,10 @@
         <v>18</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>20</v>
@@ -4175,10 +4235,10 @@
         <v>22</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>24</v>
+        <v>158</v>
       </c>
       <c r="L64" s="2" t="s">
         <v>25</v>
@@ -4195,25 +4255,25 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>21</v>
@@ -4222,10 +4282,10 @@
         <v>22</v>
       </c>
       <c r="J65" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="K65" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="K65" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="L65" s="2" t="s">
         <v>25</v>
@@ -4242,22 +4302,22 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>20</v>
@@ -4269,10 +4329,10 @@
         <v>22</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>24</v>
+        <v>206</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>25</v>
@@ -4289,22 +4349,22 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>20</v>
@@ -4316,16 +4376,16 @@
         <v>22</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>24</v>
+        <v>158</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="N67" s="2" t="s">
         <v>50</v>
@@ -4336,22 +4396,22 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>182</v>
+        <v>209</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>20</v>
@@ -4363,16 +4423,16 @@
         <v>22</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>198</v>
+        <v>24</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>24</v>
+        <v>206</v>
       </c>
       <c r="L68" s="2" t="s">
         <v>49</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="N68" s="2" t="s">
         <v>50</v>
@@ -4383,22 +4443,22 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>182</v>
+        <v>212</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>20</v>
@@ -4410,16 +4470,16 @@
         <v>22</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>198</v>
+        <v>24</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>24</v>
+        <v>206</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>49</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="N69" s="2" t="s">
         <v>50</v>
@@ -4430,22 +4490,22 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>182</v>
+        <v>214</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>20</v>
@@ -4457,16 +4517,16 @@
         <v>22</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>198</v>
+        <v>24</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>24</v>
+        <v>206</v>
       </c>
       <c r="L70" s="2" t="s">
         <v>49</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="N70" s="2" t="s">
         <v>50</v>
@@ -4477,22 +4537,22 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>182</v>
+        <v>216</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>20</v>
@@ -4504,16 +4564,16 @@
         <v>22</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>198</v>
+        <v>24</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>24</v>
+        <v>206</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>49</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="N71" s="2" t="s">
         <v>50</v>
@@ -4524,22 +4584,22 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>182</v>
+        <v>218</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>20</v>
@@ -4551,16 +4611,16 @@
         <v>22</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>198</v>
+        <v>24</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="N72" s="2" t="s">
         <v>50</v>
@@ -4571,22 +4631,22 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>182</v>
+        <v>220</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>20</v>
@@ -4598,16 +4658,16 @@
         <v>22</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>198</v>
+        <v>24</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="N73" s="2" t="s">
         <v>50</v>
@@ -4618,37 +4678,37 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="L74" s="2" t="s">
         <v>25</v>
@@ -4665,22 +4725,22 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>20</v>
@@ -4692,10 +4752,10 @@
         <v>22</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>24</v>
+        <v>158</v>
       </c>
       <c r="L75" s="2" t="s">
         <v>25</v>
@@ -4712,22 +4772,22 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>20</v>
@@ -4739,10 +4799,10 @@
         <v>22</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="L76" s="2" t="s">
         <v>25</v>
@@ -4759,22 +4819,22 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>20</v>
@@ -4786,10 +4846,10 @@
         <v>22</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="L77" s="2" t="s">
         <v>25</v>
@@ -4806,22 +4866,22 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>20</v>
@@ -4833,10 +4893,10 @@
         <v>22</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="L78" s="2" t="s">
         <v>25</v>
@@ -4853,22 +4913,22 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>69</v>
+        <v>234</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>20</v>
@@ -4880,10 +4940,10 @@
         <v>22</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="L79" s="2" t="s">
         <v>25</v>
@@ -4900,22 +4960,22 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>69</v>
+        <v>236</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>20</v>
@@ -4927,10 +4987,10 @@
         <v>22</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="L80" s="2" t="s">
         <v>25</v>
@@ -4958,23 +5018,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="B2" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="D2" t="s">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="E2" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -4982,16 +5042,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>226</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -5002,15 +5062,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>320.8</v>
+        <v>41.35</v>
       </c>
       <c r="J5" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>227</v>
+        <v>247</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -5023,7 +5083,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K23">
         <v>1</v>
@@ -5031,7 +5091,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -5062,12 +5122,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>229</v>
+        <v>249</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="B2">
         <v>79</v>
@@ -5081,35 +5141,35 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>320.8</v>
+        <v>41.35</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -5117,22 +5177,22 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E10">
         <v>59</v>
       </c>
       <c r="G10" t="s">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -5147,15 +5207,15 @@
         <v>50</v>
       </c>
       <c r="Q10">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>138</v>
+        <v>30</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" t="s">
         <v>17</v>
@@ -5164,7 +5224,7 @@
         <v>11</v>
       </c>
       <c r="G11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H11">
         <v>7</v>
@@ -5173,30 +5233,30 @@
         <v>26</v>
       </c>
       <c r="K11">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="M11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="N11">
         <v>11</v>
       </c>
       <c r="P11" t="s">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="Q11">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="E12">
         <v>6</v>
@@ -5208,13 +5268,13 @@
         <v>71</v>
       </c>
       <c r="J12" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="K12">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -5223,18 +5283,24 @@
         <v>27</v>
       </c>
       <c r="Q12">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="4:17" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>146</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
       <c r="D13" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="E13">
         <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -5245,28 +5311,22 @@
       <c r="N13">
         <v>12</v>
       </c>
-      <c r="P13" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q13">
-        <v>23</v>
-      </c>
     </row>
     <row r="14" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D14" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="N14">
         <v>1</v>
@@ -5274,7 +5334,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="N15">
         <v>2</v>
@@ -5282,7 +5342,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -5290,7 +5350,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -5298,10 +5358,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -5309,7 +5369,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -5317,142 +5377,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>156</v>
+        <v>40</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>337</v>
+        <v>412</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>157</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>204</v>
+        <v>47</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>334</v>
+        <v>412</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>205</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>137</v>
+        <v>64</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>138</v>
+        <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>300</v>
+        <v>412</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>139</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>284</v>
+        <v>412</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>161</v>
+        <v>75</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>162</v>
+        <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>274</v>
+        <v>412</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>165</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>15</v>
+        <v>88</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>412</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>19</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>412</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>45</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>52</v>
+        <v>124</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>412</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>53</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>55</v>
+        <v>127</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>412</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>56</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>58</v>
+        <v>137</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>412</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
